--- a/tests/xyz/Example_GRF/Example_output_files/PSD_Plot.xlsx
+++ b/tests/xyz/Example_GRF/Example_output_files/PSD_Plot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PrO-VAT/tests/xyz/Example_GRF/Example_output_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/xyz/Example_GRF/Example_output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF2FF1A6-D388-4C94-AC88-049432447E45}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970AE089-572C-4C06-AD9F-D3E4D2D2FF26}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
@@ -405,211 +405,211 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99702000000000002</c:v>
+                  <c:v>0.99397999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99151999999999996</c:v>
+                  <c:v>0.98512</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.98204999999999998</c:v>
+                  <c:v>0.97882999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.97740000000000005</c:v>
+                  <c:v>0.97313000000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.97133000000000003</c:v>
+                  <c:v>0.96972000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.96794000000000002</c:v>
+                  <c:v>0.95891000000000004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.95489000000000002</c:v>
+                  <c:v>0.95077</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.94357000000000002</c:v>
+                  <c:v>0.93461000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.93020999999999998</c:v>
+                  <c:v>0.92522000000000004</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.92273000000000005</c:v>
+                  <c:v>0.91995000000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.91669</c:v>
+                  <c:v>0.91247999999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.91056000000000004</c:v>
+                  <c:v>0.90146999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.89666000000000001</c:v>
+                  <c:v>0.88927</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.88382000000000005</c:v>
+                  <c:v>0.87810999999999995</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.87180999999999997</c:v>
+                  <c:v>0.86446000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.85997000000000001</c:v>
+                  <c:v>0.85396000000000005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.85045000000000004</c:v>
+                  <c:v>0.84306000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83948999999999996</c:v>
+                  <c:v>0.82665999999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.81962000000000002</c:v>
+                  <c:v>0.81106999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.80657000000000001</c:v>
+                  <c:v>0.80047999999999997</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.79744000000000004</c:v>
+                  <c:v>0.78708</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.78081999999999996</c:v>
+                  <c:v>0.76815999999999995</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.76088</c:v>
+                  <c:v>0.74848000000000003</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.74102000000000001</c:v>
+                  <c:v>0.72977000000000003</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.72102999999999995</c:v>
+                  <c:v>0.70698000000000005</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.69672999999999996</c:v>
+                  <c:v>0.68406</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.67691000000000001</c:v>
+                  <c:v>0.66644000000000003</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.65990000000000004</c:v>
+                  <c:v>0.64883000000000002</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.64127000000000001</c:v>
+                  <c:v>0.62602999999999998</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.61597999999999997</c:v>
+                  <c:v>0.60145999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.59314</c:v>
+                  <c:v>0.57762000000000002</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.56611999999999996</c:v>
+                  <c:v>0.54700000000000004</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.53496999999999995</c:v>
+                  <c:v>0.51949000000000001</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.50963999999999998</c:v>
+                  <c:v>0.49268000000000001</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.48088999999999998</c:v>
+                  <c:v>0.46327000000000002</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.45129000000000002</c:v>
+                  <c:v>0.43291000000000002</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.4214</c:v>
+                  <c:v>0.40447</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3921</c:v>
+                  <c:v>0.37546000000000002</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.36514000000000002</c:v>
+                  <c:v>0.34865000000000002</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.33654000000000001</c:v>
+                  <c:v>0.31862000000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.30670999999999998</c:v>
+                  <c:v>0.29010999999999998</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.27916000000000002</c:v>
+                  <c:v>0.26069999999999999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.24903</c:v>
+                  <c:v>0.23300999999999999</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.22253000000000001</c:v>
+                  <c:v>0.20721999999999999</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.19755</c:v>
+                  <c:v>0.18259</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.17302000000000001</c:v>
+                  <c:v>0.15947</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.15215999999999999</c:v>
+                  <c:v>0.13836999999999999</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.12917000000000001</c:v>
+                  <c:v>0.11720999999999999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.11064</c:v>
+                  <c:v>9.9479999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>9.1950000000000004E-2</c:v>
+                  <c:v>8.3309999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>7.7229999999999993E-2</c:v>
+                  <c:v>6.8229999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.3750000000000001E-2</c:v>
+                  <c:v>5.7270000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>5.3469999999999997E-2</c:v>
+                  <c:v>4.6550000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.2299999999999997E-2</c:v>
+                  <c:v>3.6769999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>3.2599999999999997E-2</c:v>
+                  <c:v>2.7990000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2.4649999999999998E-2</c:v>
+                  <c:v>2.1989999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.9900000000000001E-2</c:v>
+                  <c:v>1.643E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.482E-2</c:v>
+                  <c:v>1.242E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.1299999999999999E-2</c:v>
+                  <c:v>9.5899999999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>7.7999999999999996E-3</c:v>
+                  <c:v>6.7200000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>5.7299999999999999E-3</c:v>
+                  <c:v>5.0099999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>4.5399999999999998E-3</c:v>
+                  <c:v>3.8999999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3.6600000000000001E-3</c:v>
+                  <c:v>3.3899999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>3.0599999999999998E-3</c:v>
+                  <c:v>2.8900000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2.8300000000000001E-3</c:v>
+                  <c:v>2.2000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1.82E-3</c:v>
+                  <c:v>1.47E-3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1.0499999999999999E-3</c:v>
+                  <c:v>6.4000000000000005E-4</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>6.4000000000000005E-4</c:v>
+                  <c:v>4.2999999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2.2000000000000001E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0</c:v>
@@ -926,214 +926,214 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.11919999999999946</c:v>
+                  <c:v>0.24080000000000135</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22000000000000222</c:v>
+                  <c:v>0.35439999999999883</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3787999999999988</c:v>
+                  <c:v>0.25160000000000049</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.18599999999999711</c:v>
+                  <c:v>0.2279999999999969</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.24280000000000057</c:v>
+                  <c:v>0.13640000000000085</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.13560000000000036</c:v>
+                  <c:v>0.43240000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5219999999999998</c:v>
+                  <c:v>0.32560000000000117</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.45280000000000048</c:v>
+                  <c:v>0.64639999999999898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5344000000000011</c:v>
+                  <c:v>0.37560000000000004</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.29919999999999697</c:v>
+                  <c:v>0.21079999999999968</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.24160000000000159</c:v>
+                  <c:v>0.29880000000000323</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.24519999999999961</c:v>
+                  <c:v>0.44040000000000012</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.55600000000000049</c:v>
+                  <c:v>0.4879999999999991</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.51359999999999806</c:v>
+                  <c:v>0.44640000000000196</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.4804000000000026</c:v>
+                  <c:v>0.54599999999999715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.47359999999999802</c:v>
+                  <c:v>0.41999999999999776</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.38080000000000025</c:v>
+                  <c:v>0.43600000000000239</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.43840000000000284</c:v>
+                  <c:v>0.65600000000000269</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.79479999999999706</c:v>
+                  <c:v>0.62359999999999915</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.5219999999999998</c:v>
+                  <c:v>0.42359999999999914</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.36519999999999853</c:v>
+                  <c:v>0.53599999999999826</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.6648000000000055</c:v>
+                  <c:v>0.75680000000000458</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.79759999999999764</c:v>
+                  <c:v>0.78719999999999613</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.79439999999999888</c:v>
+                  <c:v>0.74839999999999951</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.79960000000000186</c:v>
+                  <c:v>0.9115999999999983</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.97199999999999864</c:v>
+                  <c:v>0.91680000000000128</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.79280000000000073</c:v>
+                  <c:v>0.70480000000000131</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.68039999999999512</c:v>
+                  <c:v>0.70439999999999681</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.74520000000000408</c:v>
+                  <c:v>0.91200000000000492</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.0116000000000049</c:v>
+                  <c:v>0.98280000000000267</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.91359999999999397</c:v>
+                  <c:v>0.95359999999999379</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.0808000000000055</c:v>
+                  <c:v>1.2248000000000037</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.2459999999999938</c:v>
+                  <c:v>1.1003999999999956</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.0132000000000021</c:v>
+                  <c:v>1.0724000000000038</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.1500000000000039</c:v>
+                  <c:v>1.1764000000000039</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.1839999999999922</c:v>
+                  <c:v>1.2143999999999935</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.1956000000000053</c:v>
+                  <c:v>1.1376000000000048</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.1719999999999935</c:v>
+                  <c:v>1.160399999999993</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.0784000000000031</c:v>
+                  <c:v>1.0724000000000038</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.1440000000000046</c:v>
+                  <c:v>1.2012000000000043</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.1931999999999945</c:v>
+                  <c:v>1.1403999999999954</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.1020000000000025</c:v>
+                  <c:v>1.1764000000000039</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.2051999999999943</c:v>
+                  <c:v>1.1075999999999937</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.0600000000000036</c:v>
+                  <c:v>1.0316000000000041</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.99920000000000364</c:v>
+                  <c:v>0.98520000000000296</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.98119999999999463</c:v>
+                  <c:v>0.92479999999999518</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83440000000000369</c:v>
+                  <c:v>0.8440000000000033</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.91959999999999442</c:v>
+                  <c:v>0.84639999999999538</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.74120000000000286</c:v>
+                  <c:v>0.70920000000000238</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.7476000000000026</c:v>
+                  <c:v>0.64680000000000248</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.58879999999999733</c:v>
+                  <c:v>0.60319999999999663</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.53920000000000634</c:v>
+                  <c:v>0.43840000000000534</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.41119999999999801</c:v>
+                  <c:v>0.42879999999999774</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.44680000000000158</c:v>
+                  <c:v>0.39120000000000155</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.38799999999999796</c:v>
+                  <c:v>0.35119999999999796</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.31800000000000106</c:v>
+                  <c:v>0.24000000000000093</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.19000000000000056</c:v>
+                  <c:v>0.22240000000000074</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.20319999999999896</c:v>
+                  <c:v>0.16039999999999913</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.14080000000000054</c:v>
+                  <c:v>0.11320000000000044</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.13999999999999924</c:v>
+                  <c:v>0.11479999999999936</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>8.280000000000029E-2</c:v>
+                  <c:v>6.8400000000000266E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>4.760000000000017E-2</c:v>
+                  <c:v>4.4400000000000155E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3.5199999999999801E-2</c:v>
+                  <c:v>2.0399999999999894E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2.4000000000000098E-2</c:v>
+                  <c:v>2.0000000000000052E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>9.1999999999999409E-3</c:v>
+                  <c:v>2.7599999999999857E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4.0400000000000144E-2</c:v>
+                  <c:v>2.9200000000000111E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>3.0800000000000112E-2</c:v>
+                  <c:v>3.3200000000000111E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1.6400000000000053E-2</c:v>
+                  <c:v>8.4000000000000324E-3</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.6799999999999763E-2</c:v>
+                  <c:v>1.7199999999999754E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>8.8000000000000318E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0</c:v>
@@ -2196,10 +2196,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2577,11 +2573,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="C4">
-        <v>0.99702000000000002</v>
+        <v>0.99397999999999997</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D67" si="1">(C3-C4)/(B4-B3)</f>
-        <v>0.11919999999999946</v>
+        <v>0.24080000000000135</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2593,11 +2589,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="C5">
-        <v>0.99151999999999996</v>
+        <v>0.98512</v>
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>0.22000000000000222</v>
+        <v>0.35439999999999883</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,11 +2605,11 @@
         <v>0.39</v>
       </c>
       <c r="C6">
-        <v>0.98204999999999998</v>
+        <v>0.97882999999999998</v>
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>0.3787999999999988</v>
+        <v>0.25160000000000049</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2625,11 +2621,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="C7">
-        <v>0.97740000000000005</v>
+        <v>0.97313000000000005</v>
       </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>0.18599999999999711</v>
+        <v>0.2279999999999969</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2641,11 +2637,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="C8">
-        <v>0.97133000000000003</v>
+        <v>0.96972000000000003</v>
       </c>
       <c r="D8">
         <f t="shared" si="1"/>
-        <v>0.24280000000000057</v>
+        <v>0.13640000000000085</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2657,11 +2653,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="C9">
-        <v>0.96794000000000002</v>
+        <v>0.95891000000000004</v>
       </c>
       <c r="D9">
         <f t="shared" si="1"/>
-        <v>0.13560000000000036</v>
+        <v>0.43240000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2673,11 +2669,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="C10">
-        <v>0.95489000000000002</v>
+        <v>0.95077</v>
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>0.5219999999999998</v>
+        <v>0.32560000000000117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2689,11 +2685,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="C11">
-        <v>0.94357000000000002</v>
+        <v>0.93461000000000005</v>
       </c>
       <c r="D11">
         <f t="shared" si="1"/>
-        <v>0.45280000000000048</v>
+        <v>0.64639999999999898</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2705,11 +2701,11 @@
         <v>0.54</v>
       </c>
       <c r="C12">
-        <v>0.93020999999999998</v>
+        <v>0.92522000000000004</v>
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
-        <v>0.5344000000000011</v>
+        <v>0.37560000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2721,11 +2717,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="C13">
-        <v>0.92273000000000005</v>
+        <v>0.91995000000000005</v>
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>0.29919999999999697</v>
+        <v>0.21079999999999968</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2737,11 +2733,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="C14">
-        <v>0.91669</v>
+        <v>0.91247999999999996</v>
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>0.24160000000000159</v>
+        <v>0.29880000000000323</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2753,11 +2749,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C15">
-        <v>0.91056000000000004</v>
+        <v>0.90146999999999999</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>0.24519999999999961</v>
+        <v>0.44040000000000012</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2769,11 +2765,11 @@
         <v>0.64</v>
       </c>
       <c r="C16">
-        <v>0.89666000000000001</v>
+        <v>0.88927</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>0.55600000000000049</v>
+        <v>0.4879999999999991</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2785,11 +2781,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="C17">
-        <v>0.88382000000000005</v>
+        <v>0.87810999999999995</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>0.51359999999999806</v>
+        <v>0.44640000000000196</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2801,11 +2797,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="C18">
-        <v>0.87180999999999997</v>
+        <v>0.86446000000000001</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>0.4804000000000026</v>
+        <v>0.54599999999999715</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2817,11 +2813,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="C19">
-        <v>0.85997000000000001</v>
+        <v>0.85396000000000005</v>
       </c>
       <c r="D19">
         <f t="shared" si="1"/>
-        <v>0.47359999999999802</v>
+        <v>0.41999999999999776</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2833,11 +2829,11 @@
         <v>0.74</v>
       </c>
       <c r="C20">
-        <v>0.85045000000000004</v>
+        <v>0.84306000000000003</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.38080000000000025</v>
+        <v>0.43600000000000239</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2849,11 +2845,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="C21">
-        <v>0.83948999999999996</v>
+        <v>0.82665999999999995</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0.43840000000000284</v>
+        <v>0.65600000000000269</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2865,11 +2861,11 @@
         <v>0.79</v>
       </c>
       <c r="C22">
-        <v>0.81962000000000002</v>
+        <v>0.81106999999999996</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0.79479999999999706</v>
+        <v>0.62359999999999915</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2881,11 +2877,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="C23">
-        <v>0.80657000000000001</v>
+        <v>0.80047999999999997</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0.5219999999999998</v>
+        <v>0.42359999999999914</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2897,11 +2893,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="C24">
-        <v>0.79744000000000004</v>
+        <v>0.78708</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0.36519999999999853</v>
+        <v>0.53599999999999826</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2913,11 +2909,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="C25">
-        <v>0.78081999999999996</v>
+        <v>0.76815999999999995</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.6648000000000055</v>
+        <v>0.75680000000000458</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2929,11 +2925,11 @@
         <v>0.89</v>
       </c>
       <c r="C26">
-        <v>0.76088</v>
+        <v>0.74848000000000003</v>
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>0.79759999999999764</v>
+        <v>0.78719999999999613</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2945,11 +2941,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="C27">
-        <v>0.74102000000000001</v>
+        <v>0.72977000000000003</v>
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>0.79439999999999888</v>
+        <v>0.74839999999999951</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2961,11 +2957,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="C28">
-        <v>0.72102999999999995</v>
+        <v>0.70698000000000005</v>
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>0.79960000000000186</v>
+        <v>0.9115999999999983</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -2977,11 +2973,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="C29">
-        <v>0.69672999999999996</v>
+        <v>0.68406</v>
       </c>
       <c r="D29">
         <f t="shared" si="1"/>
-        <v>0.97199999999999864</v>
+        <v>0.91680000000000128</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -2993,11 +2989,11 @@
         <v>0.99</v>
       </c>
       <c r="C30">
-        <v>0.67691000000000001</v>
+        <v>0.66644000000000003</v>
       </c>
       <c r="D30">
         <f t="shared" si="1"/>
-        <v>0.79280000000000073</v>
+        <v>0.70480000000000131</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3009,11 +3005,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="C31">
-        <v>0.65990000000000004</v>
+        <v>0.64883000000000002</v>
       </c>
       <c r="D31">
         <f t="shared" si="1"/>
-        <v>0.68039999999999512</v>
+        <v>0.70439999999999681</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -3026,11 +3022,11 @@
         <v>1.04</v>
       </c>
       <c r="C32">
-        <v>0.64127000000000001</v>
+        <v>0.62602999999999998</v>
       </c>
       <c r="D32">
         <f t="shared" si="1"/>
-        <v>0.74520000000000408</v>
+        <v>0.91200000000000492</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -3043,11 +3039,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="C33">
-        <v>0.61597999999999997</v>
+        <v>0.60145999999999999</v>
       </c>
       <c r="D33">
         <f t="shared" si="1"/>
-        <v>1.0116000000000049</v>
+        <v>0.98280000000000267</v>
       </c>
       <c r="H33" s="1"/>
     </row>
@@ -3060,11 +3056,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="C34">
-        <v>0.59314</v>
+        <v>0.57762000000000002</v>
       </c>
       <c r="D34">
         <f t="shared" si="1"/>
-        <v>0.91359999999999397</v>
+        <v>0.95359999999999379</v>
       </c>
       <c r="H34" s="1"/>
     </row>
@@ -3077,11 +3073,11 @@
         <v>1.115</v>
       </c>
       <c r="C35">
-        <v>0.56611999999999996</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="D35">
         <f t="shared" si="1"/>
-        <v>1.0808000000000055</v>
+        <v>1.2248000000000037</v>
       </c>
       <c r="H35" s="1"/>
     </row>
@@ -3094,11 +3090,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="C36">
-        <v>0.53496999999999995</v>
+        <v>0.51949000000000001</v>
       </c>
       <c r="D36">
         <f t="shared" si="1"/>
-        <v>1.2459999999999938</v>
+        <v>1.1003999999999956</v>
       </c>
       <c r="H36" s="1"/>
     </row>
@@ -3111,11 +3107,11 @@
         <v>1.165</v>
       </c>
       <c r="C37">
-        <v>0.50963999999999998</v>
+        <v>0.49268000000000001</v>
       </c>
       <c r="D37">
         <f t="shared" si="1"/>
-        <v>1.0132000000000021</v>
+        <v>1.0724000000000038</v>
       </c>
       <c r="H37" s="1"/>
     </row>
@@ -3128,11 +3124,11 @@
         <v>1.19</v>
       </c>
       <c r="C38">
-        <v>0.48088999999999998</v>
+        <v>0.46327000000000002</v>
       </c>
       <c r="D38">
         <f t="shared" si="1"/>
-        <v>1.1500000000000039</v>
+        <v>1.1764000000000039</v>
       </c>
       <c r="H38" s="1"/>
     </row>
@@ -3145,11 +3141,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="C39">
-        <v>0.45129000000000002</v>
+        <v>0.43291000000000002</v>
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>1.1839999999999922</v>
+        <v>1.2143999999999935</v>
       </c>
       <c r="H39" s="1"/>
     </row>
@@ -3162,11 +3158,11 @@
         <v>1.24</v>
       </c>
       <c r="C40">
-        <v>0.4214</v>
+        <v>0.40447</v>
       </c>
       <c r="D40">
         <f t="shared" si="1"/>
-        <v>1.1956000000000053</v>
+        <v>1.1376000000000048</v>
       </c>
       <c r="H40" s="1"/>
     </row>
@@ -3179,11 +3175,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="C41">
-        <v>0.3921</v>
+        <v>0.37546000000000002</v>
       </c>
       <c r="D41">
         <f t="shared" si="1"/>
-        <v>1.1719999999999935</v>
+        <v>1.160399999999993</v>
       </c>
       <c r="H41" s="1"/>
     </row>
@@ -3196,11 +3192,11 @@
         <v>1.29</v>
       </c>
       <c r="C42">
-        <v>0.36514000000000002</v>
+        <v>0.34865000000000002</v>
       </c>
       <c r="D42">
         <f t="shared" si="1"/>
-        <v>1.0784000000000031</v>
+        <v>1.0724000000000038</v>
       </c>
       <c r="H42" s="1"/>
     </row>
@@ -3213,11 +3209,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="C43">
-        <v>0.33654000000000001</v>
+        <v>0.31862000000000001</v>
       </c>
       <c r="D43">
         <f t="shared" si="1"/>
-        <v>1.1440000000000046</v>
+        <v>1.2012000000000043</v>
       </c>
       <c r="H43" s="1"/>
     </row>
@@ -3230,11 +3226,11 @@
         <v>1.34</v>
       </c>
       <c r="C44">
-        <v>0.30670999999999998</v>
+        <v>0.29010999999999998</v>
       </c>
       <c r="D44">
         <f t="shared" si="1"/>
-        <v>1.1931999999999945</v>
+        <v>1.1403999999999954</v>
       </c>
       <c r="H44" s="1"/>
     </row>
@@ -3247,11 +3243,11 @@
         <v>1.365</v>
       </c>
       <c r="C45">
-        <v>0.27916000000000002</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="D45">
         <f t="shared" si="1"/>
-        <v>1.1020000000000025</v>
+        <v>1.1764000000000039</v>
       </c>
       <c r="H45" s="1"/>
     </row>
@@ -3264,11 +3260,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="C46">
-        <v>0.24903</v>
+        <v>0.23300999999999999</v>
       </c>
       <c r="D46">
         <f t="shared" si="1"/>
-        <v>1.2051999999999943</v>
+        <v>1.1075999999999937</v>
       </c>
       <c r="H46" s="1"/>
     </row>
@@ -3281,11 +3277,11 @@
         <v>1.415</v>
       </c>
       <c r="C47">
-        <v>0.22253000000000001</v>
+        <v>0.20721999999999999</v>
       </c>
       <c r="D47">
         <f t="shared" si="1"/>
-        <v>1.0600000000000036</v>
+        <v>1.0316000000000041</v>
       </c>
       <c r="H47" s="1"/>
     </row>
@@ -3298,11 +3294,11 @@
         <v>1.44</v>
       </c>
       <c r="C48">
-        <v>0.19755</v>
+        <v>0.18259</v>
       </c>
       <c r="D48">
         <f t="shared" si="1"/>
-        <v>0.99920000000000364</v>
+        <v>0.98520000000000296</v>
       </c>
       <c r="H48" s="1"/>
     </row>
@@ -3315,11 +3311,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="C49">
-        <v>0.17302000000000001</v>
+        <v>0.15947</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>0.98119999999999463</v>
+        <v>0.92479999999999518</v>
       </c>
       <c r="H49" s="1"/>
     </row>
@@ -3332,11 +3328,11 @@
         <v>1.49</v>
       </c>
       <c r="C50">
-        <v>0.15215999999999999</v>
+        <v>0.13836999999999999</v>
       </c>
       <c r="D50">
         <f t="shared" si="1"/>
-        <v>0.83440000000000369</v>
+        <v>0.8440000000000033</v>
       </c>
       <c r="H50" s="1"/>
     </row>
@@ -3349,11 +3345,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="C51">
-        <v>0.12917000000000001</v>
+        <v>0.11720999999999999</v>
       </c>
       <c r="D51">
         <f t="shared" si="1"/>
-        <v>0.91959999999999442</v>
+        <v>0.84639999999999538</v>
       </c>
       <c r="H51" s="1"/>
     </row>
@@ -3366,11 +3362,11 @@
         <v>1.54</v>
       </c>
       <c r="C52">
-        <v>0.11064</v>
+        <v>9.9479999999999999E-2</v>
       </c>
       <c r="D52">
         <f t="shared" si="1"/>
-        <v>0.74120000000000286</v>
+        <v>0.70920000000000238</v>
       </c>
       <c r="H52" s="1"/>
     </row>
@@ -3383,11 +3379,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="C53">
-        <v>9.1950000000000004E-2</v>
+        <v>8.3309999999999995E-2</v>
       </c>
       <c r="D53">
         <f t="shared" si="1"/>
-        <v>0.7476000000000026</v>
+        <v>0.64680000000000248</v>
       </c>
       <c r="H53" s="1"/>
     </row>
@@ -3400,11 +3396,11 @@
         <v>1.59</v>
       </c>
       <c r="C54">
-        <v>7.7229999999999993E-2</v>
+        <v>6.8229999999999999E-2</v>
       </c>
       <c r="D54">
         <f t="shared" si="1"/>
-        <v>0.58879999999999733</v>
+        <v>0.60319999999999663</v>
       </c>
       <c r="H54" s="1"/>
     </row>
@@ -3417,11 +3413,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="C55">
-        <v>6.3750000000000001E-2</v>
+        <v>5.7270000000000001E-2</v>
       </c>
       <c r="D55">
         <f t="shared" si="1"/>
-        <v>0.53920000000000634</v>
+        <v>0.43840000000000534</v>
       </c>
       <c r="H55" s="1"/>
     </row>
@@ -3434,11 +3430,11 @@
         <v>1.64</v>
       </c>
       <c r="C56">
-        <v>5.3469999999999997E-2</v>
+        <v>4.6550000000000001E-2</v>
       </c>
       <c r="D56">
         <f t="shared" si="1"/>
-        <v>0.41119999999999801</v>
+        <v>0.42879999999999774</v>
       </c>
       <c r="H56" s="1"/>
     </row>
@@ -3451,11 +3447,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="C57">
-        <v>4.2299999999999997E-2</v>
+        <v>3.6769999999999997E-2</v>
       </c>
       <c r="D57">
         <f t="shared" si="1"/>
-        <v>0.44680000000000158</v>
+        <v>0.39120000000000155</v>
       </c>
       <c r="H57" s="1"/>
     </row>
@@ -3468,11 +3464,11 @@
         <v>1.69</v>
       </c>
       <c r="C58">
-        <v>3.2599999999999997E-2</v>
+        <v>2.7990000000000001E-2</v>
       </c>
       <c r="D58">
         <f t="shared" si="1"/>
-        <v>0.38799999999999796</v>
+        <v>0.35119999999999796</v>
       </c>
       <c r="H58" s="1"/>
     </row>
@@ -3485,11 +3481,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="C59">
-        <v>2.4649999999999998E-2</v>
+        <v>2.1989999999999999E-2</v>
       </c>
       <c r="D59">
         <f t="shared" si="1"/>
-        <v>0.31800000000000106</v>
+        <v>0.24000000000000093</v>
       </c>
       <c r="H59" s="1"/>
     </row>
@@ -3502,11 +3498,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="C60">
-        <v>1.9900000000000001E-2</v>
+        <v>1.643E-2</v>
       </c>
       <c r="D60">
         <f t="shared" si="1"/>
-        <v>0.19000000000000056</v>
+        <v>0.22240000000000074</v>
       </c>
       <c r="H60" s="1"/>
     </row>
@@ -3519,11 +3515,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="C61">
-        <v>1.482E-2</v>
+        <v>1.242E-2</v>
       </c>
       <c r="D61">
         <f t="shared" si="1"/>
-        <v>0.20319999999999896</v>
+        <v>0.16039999999999913</v>
       </c>
       <c r="H61" s="1"/>
     </row>
@@ -3536,11 +3532,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="C62">
-        <v>1.1299999999999999E-2</v>
+        <v>9.5899999999999996E-3</v>
       </c>
       <c r="D62">
         <f t="shared" si="1"/>
-        <v>0.14080000000000054</v>
+        <v>0.11320000000000044</v>
       </c>
       <c r="H62" s="1"/>
     </row>
@@ -3553,11 +3549,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="C63">
-        <v>7.7999999999999996E-3</v>
+        <v>6.7200000000000003E-3</v>
       </c>
       <c r="D63">
         <f t="shared" si="1"/>
-        <v>0.13999999999999924</v>
+        <v>0.11479999999999936</v>
       </c>
       <c r="H63" s="1"/>
     </row>
@@ -3570,11 +3566,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="C64">
-        <v>5.7299999999999999E-3</v>
+        <v>5.0099999999999997E-3</v>
       </c>
       <c r="D64">
         <f t="shared" si="1"/>
-        <v>8.280000000000029E-2</v>
+        <v>6.8400000000000266E-2</v>
       </c>
       <c r="H64" s="1"/>
     </row>
@@ -3587,11 +3583,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="C65">
-        <v>4.5399999999999998E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="D65">
         <f t="shared" si="1"/>
-        <v>4.760000000000017E-2</v>
+        <v>4.4400000000000155E-2</v>
       </c>
       <c r="H65" s="1"/>
     </row>
@@ -3604,11 +3600,11 @@
         <v>1.89</v>
       </c>
       <c r="C66">
-        <v>3.6600000000000001E-3</v>
+        <v>3.3899999999999998E-3</v>
       </c>
       <c r="D66">
         <f t="shared" si="1"/>
-        <v>3.5199999999999801E-2</v>
+        <v>2.0399999999999894E-2</v>
       </c>
       <c r="H66" s="1"/>
     </row>
@@ -3621,11 +3617,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="C67">
-        <v>3.0599999999999998E-3</v>
+        <v>2.8900000000000002E-3</v>
       </c>
       <c r="D67">
         <f t="shared" si="1"/>
-        <v>2.4000000000000098E-2</v>
+        <v>2.0000000000000052E-2</v>
       </c>
       <c r="H67" s="1"/>
     </row>
@@ -3638,11 +3634,11 @@
         <v>1.94</v>
       </c>
       <c r="C68">
-        <v>2.8300000000000001E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="D68">
         <f t="shared" ref="D68:D75" si="3">(C67-C68)/(B68-B67)</f>
-        <v>9.1999999999999409E-3</v>
+        <v>2.7599999999999857E-2</v>
       </c>
       <c r="H68" s="1"/>
     </row>
@@ -3655,11 +3651,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="C69">
-        <v>1.82E-3</v>
+        <v>1.47E-3</v>
       </c>
       <c r="D69">
         <f t="shared" si="3"/>
-        <v>4.0400000000000144E-2</v>
+        <v>2.9200000000000111E-2</v>
       </c>
       <c r="H69" s="1"/>
     </row>
@@ -3672,11 +3668,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="C70">
-        <v>1.0499999999999999E-3</v>
+        <v>6.4000000000000005E-4</v>
       </c>
       <c r="D70">
         <f t="shared" si="3"/>
-        <v>3.0800000000000112E-2</v>
+        <v>3.3200000000000111E-2</v>
       </c>
       <c r="H70" s="1"/>
     </row>
@@ -3689,11 +3685,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="C71">
-        <v>6.4000000000000005E-4</v>
+        <v>4.2999999999999999E-4</v>
       </c>
       <c r="D71">
         <f t="shared" si="3"/>
-        <v>1.6400000000000053E-2</v>
+        <v>8.4000000000000324E-3</v>
       </c>
       <c r="H71" s="1"/>
     </row>
@@ -3706,11 +3702,11 @@
         <v>2.04</v>
       </c>
       <c r="C72">
-        <v>2.2000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <f t="shared" si="3"/>
-        <v>1.6799999999999763E-2</v>
+        <v>1.7199999999999754E-2</v>
       </c>
       <c r="H72" s="1"/>
     </row>
@@ -3727,7 +3723,7 @@
       </c>
       <c r="D73">
         <f t="shared" si="3"/>
-        <v>8.8000000000000318E-3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1"/>
     </row>

--- a/tests/xyz/Example_GRF/Example_output_files/PSD_Plot.xlsx
+++ b/tests/xyz/Example_GRF/Example_output_files/PSD_Plot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/xyz/Example_GRF/Example_output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970AE089-572C-4C06-AD9F-D3E4D2D2FF26}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A23DF20E-2580-4990-BB97-B8DBACC1CB65}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
@@ -2196,6 +2196,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
